--- a/output/2026-09-13_23_Croazia_Primorsko-goranska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-13_23_Croazia_Primorsko-goranska_ATEX_Equipment-Services.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Specializzata esclusivamente in protezione antiesplosione: ispezione Ex, manutenzione unità ATEX, test elettrici/strumentali/non elettrici su impianti e attrezzature Ex, gas detection. Confermata da fonti esterne (companywall.hr).</t>
+          <t>Specializzata esclusivamente in protezione antiesplosione: ispezione Ex, manutenzione unità ATEX, test elettrici/strumentali/non elettrici su impianti e attrezzature Ex, gas detection. Confermata da fonti esterne (companywall.hr). [DUPLICATO — vedi anche: 2026-09-13_16_Croazia_Bjelovarsko-bilogorska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">

--- a/output/2026-09-13_23_Croazia_Primorsko-goranska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-13_23_Croazia_Primorsko-goranska_ATEX_Equipment-Services.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
